--- a/data/trans_dic/P1801_2016_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1801_2016_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,35%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,94; 54,84</t>
+          <t>42,87; 54,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,84; 72,93</t>
+          <t>57,97; 68,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,31; 59,42</t>
+          <t>47,02; 59,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,82; 75,93</t>
+          <t>66,92; 75,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,96; 55,12</t>
+          <t>46,66; 55,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,84; 72,77</t>
+          <t>63,44; 70,87</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,25; 51,24</t>
+          <t>41,98; 51,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 29,43</t>
+          <t>20,91; 29,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,81; 62,15</t>
+          <t>53,59; 62,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,04; 34,25</t>
+          <t>26,24; 33,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,06; 55,39</t>
+          <t>49,09; 55,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,62; 30,35</t>
+          <t>24,65; 30,24</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,91; 48,22</t>
+          <t>37,37; 48,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,31; 70,0</t>
+          <t>59,44; 70,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,07; 61,2</t>
+          <t>49,74; 60,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,83; 73,58</t>
+          <t>64,14; 72,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,49; 53,21</t>
+          <t>45,6; 53,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,6; 70,58</t>
+          <t>63,37; 70,12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,49; 60,63</t>
+          <t>49,92; 60,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,81; 58,66</t>
+          <t>42,86; 56,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,8; 66,27</t>
+          <t>56,37; 66,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 52,92</t>
+          <t>48,88; 58,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,1; 62,3</t>
+          <t>54,57; 62,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 53,5</t>
+          <t>47,58; 55,58</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,97; 52,45</t>
+          <t>40,03; 52,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,61; 66,58</t>
+          <t>50,11; 61,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,32; 61,35</t>
+          <t>47,59; 60,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,07; 72,49</t>
+          <t>61,73; 71,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,11; 55,02</t>
+          <t>45,32; 55,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,98; 68,24</t>
+          <t>57,53; 65,34</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,23; 58,76</t>
+          <t>46,44; 58,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,22; 66,35</t>
+          <t>54,56; 65,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,07; 65,5</t>
+          <t>53,67; 65,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,89; 73,77</t>
+          <t>63,95; 73,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,83; 60,77</t>
+          <t>51,98; 60,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,61; 68,52</t>
+          <t>60,56; 68,14</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,65; 39,41</t>
+          <t>31,72; 39,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,62; 65,44</t>
+          <t>55,19; 63,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,24; 53,05</t>
+          <t>44,9; 53,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,93; 88,63</t>
+          <t>67,5; 73,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,56; 45,46</t>
+          <t>39,64; 45,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,7; 82,65</t>
+          <t>62,58; 67,93</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,48; 54,18</t>
+          <t>46,71; 53,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32,43; 76,7</t>
+          <t>29,43; 36,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,27; 66,33</t>
+          <t>59,44; 66,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40,02; 46,22</t>
+          <t>39,56; 45,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,34; 59,54</t>
+          <t>54,23; 59,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,8; 67,02</t>
+          <t>35,58; 40,12</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44,71; 48,26</t>
+          <t>44,91; 48,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,68; 64,44</t>
+          <t>46,08; 49,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55,48; 58,78</t>
+          <t>55,38; 58,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53,4; 64,75</t>
+          <t>54,36; 57,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,62; 53,11</t>
+          <t>50,81; 53,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,85; 61,18</t>
+          <t>50,92; 53,3</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>202002</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206071</t>
+          <t>224879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>413283</t>
+          <t>426881</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>126140; 161110</t>
+          <t>125933; 160449</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>185608; 226193</t>
+          <t>184206; 219048</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136591; 171549</t>
+          <t>135759; 171432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>190625; 219933</t>
+          <t>211497; 237723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>273541; 321061</t>
+          <t>271781; 321689</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>382937; 436498</t>
+          <t>402115; 449204</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>128201</t>
+          <t>133126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155278</t>
+          <t>160942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>283478</t>
+          <t>294068</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>212356; 257498</t>
+          <t>211005; 257328</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>105445; 152563</t>
+          <t>110945; 158813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>281455; 325094</t>
+          <t>280324; 325766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138751; 175762</t>
+          <t>142901; 180832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>503152; 568077</t>
+          <t>503461; 568442</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>253952; 313127</t>
+          <t>265074; 325197</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>205440</t>
+          <t>205376</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>242802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>446627</t>
+          <t>448178</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120756; 153622</t>
+          <t>119047; 153754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>187441; 221250</t>
+          <t>187825; 223314</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168391; 205824</t>
+          <t>167284; 204179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225726; 256199</t>
+          <t>228018; 258185</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>297882; 348427</t>
+          <t>298601; 350025</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>422479; 468854</t>
+          <t>425546; 470840</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161350</t>
+          <t>185603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>225628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>362229</t>
+          <t>411231</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186785; 224292</t>
+          <t>184701; 223727</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136922; 183356</t>
+          <t>159919; 211006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>216113; 256662</t>
+          <t>218296; 258429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>127384; 251211</t>
+          <t>205741; 246423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>417249; 471744</t>
+          <t>413245; 470939</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>251428; 421170</t>
+          <t>377803; 441327</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>106197</t>
+          <t>115255</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142384</t>
+          <t>151552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>248581</t>
+          <t>266807</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82305; 110792</t>
+          <t>84554; 110277</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94033; 119004</t>
+          <t>103061; 127314</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105619; 134109</t>
+          <t>104028; 131570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131609; 151265</t>
+          <t>140267; 162531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>193875; 236495</t>
+          <t>194792; 237891</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>232364; 264357</t>
+          <t>249028; 282826</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>162308</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177547</t>
+          <t>180894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>341772</t>
+          <t>343202</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>121637; 154613</t>
+          <t>122200; 154454</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>148896; 178901</t>
+          <t>147697; 176673</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>144943; 178892</t>
+          <t>146570; 178496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>163789; 189115</t>
+          <t>168253; 193419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>277921; 325877</t>
+          <t>278711; 322693</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>318794; 360400</t>
+          <t>323274; 363742</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>379721</t>
+          <t>427117</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654905</t>
+          <t>543735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1034626</t>
+          <t>970852</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>207796; 258752</t>
+          <t>208241; 261642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>346114; 407183</t>
+          <t>395967; 456892</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>312743; 366724</t>
+          <t>310390; 366737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>584367; 751457</t>
+          <t>519074; 567914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>533155; 612720</t>
+          <t>534251; 612544</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>951061; 1215038</t>
+          <t>930284; 1009825</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>474478</t>
+          <t>260871</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>310003</t>
+          <t>354134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>784481</t>
+          <t>615006</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>361889; 421826</t>
+          <t>363639; 419305</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>301193; 712285</t>
+          <t>234838; 288667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>489637; 548033</t>
+          <t>491106; 547851</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>287251; 331759</t>
+          <t>328904; 378652</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>871993; 955394</t>
+          <t>870208; 952287</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>622312; 1103437</t>
+          <t>579770; 653779</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1517483; 1638137</t>
+          <t>1524395; 1638978</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1682575; 2227435</t>
+          <t>1626326; 1757140</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1966592; 2083332</t>
+          <t>1962823; 2088270</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1952295; 2367460</t>
+          <t>2026244; 2136118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3512610; 3685006</t>
+          <t>3525518; 3700078</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3688333; 4351924</t>
+          <t>3695188; 3868475</t>
         </is>
       </c>
     </row>
